--- a/output/StructureDefinition-BRAlergiaReacaoAdversa-1.0.xlsx
+++ b/output/StructureDefinition-BRAlergiaReacaoAdversa-1.0.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3810" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3808" uniqueCount="566">
   <si>
     <t>Property</t>
   </si>
@@ -1013,6 +1013,15 @@
     <t>gender</t>
   </si>
   <si>
+    <t>Sexo</t>
+  </si>
+  <si>
+    <t>Sexo biológico obtido por meio de exame clínico ou de outros métodos diagnósticos referente ao indivíduo da hipótese de impossibilidade de identificação.</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRSexo-1.0</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.patient.extension:unidentifiedPatient.extension:gender.id</t>
   </si>
   <si>
@@ -1062,6 +1071,12 @@
   </si>
   <si>
     <t>birthYear</t>
+  </si>
+  <si>
+    <t>Ano de nascimento estimado</t>
+  </si>
+  <si>
+    <t>Estimativa do ano de nascimento por meio de observação direta da idade do indivíduo na hipótese de impossibilidade de identificação..</t>
   </si>
   <si>
     <t>AllergyIntolerance.patient.extension:unidentifiedPatient.extension:birthYear.id</t>
@@ -1084,6 +1099,15 @@
   </si>
   <si>
     <t>reason</t>
+  </si>
+  <si>
+    <t>Justificativa da impossibilidade de identificação do indivíduo</t>
+  </si>
+  <si>
+    <t>Razão pela qual não foi possível obter os dados de identificação do indivíduo no contato assistencial.</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRJustificativaIndividuoNaoIdentificado-1.0</t>
   </si>
   <si>
     <t>AllergyIntolerance.patient.extension:unidentifiedPatient.extension:reason.id</t>
@@ -7159,10 +7183,10 @@
         <v>131</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7189,13 +7213,11 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>79</v>
+        <v>318</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
@@ -7239,10 +7261,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7348,10 +7370,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7459,10 +7481,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7488,13 +7510,13 @@
         <v>99</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7544,7 +7566,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>86</v>
@@ -7570,10 +7592,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7599,10 +7621,10 @@
         <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7653,7 +7675,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7679,13 +7701,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>312</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>79</v>
@@ -7710,10 +7732,10 @@
         <v>131</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>302</v>
+        <v>336</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>303</v>
+        <v>337</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7790,10 +7812,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7899,10 +7921,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8010,10 +8032,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8039,13 +8061,13 @@
         <v>99</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8053,7 +8075,7 @@
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>79</v>
@@ -8095,7 +8117,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>86</v>
@@ -8121,10 +8143,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8147,13 +8169,13 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8204,7 +8226,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8230,13 +8252,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>312</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>79</v>
@@ -8261,10 +8283,10 @@
         <v>131</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>302</v>
+        <v>345</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>303</v>
+        <v>346</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8291,13 +8313,11 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>79</v>
+        <v>347</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8341,10 +8361,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8450,10 +8470,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8561,10 +8581,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8590,13 +8610,13 @@
         <v>99</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8604,7 +8624,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>79</v>
@@ -8646,7 +8666,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>86</v>
@@ -8672,10 +8692,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8701,10 +8721,10 @@
         <v>152</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8755,7 +8775,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8781,10 +8801,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8810,13 +8830,13 @@
         <v>99</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8824,7 +8844,7 @@
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>79</v>
@@ -8866,7 +8886,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>86</v>
@@ -8892,10 +8912,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8918,13 +8938,13 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8975,7 +8995,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -9001,10 +9021,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9030,13 +9050,13 @@
         <v>169</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9086,7 +9106,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9095,7 +9115,7 @@
         <v>86</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>97</v>
@@ -9112,10 +9132,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9141,13 +9161,13 @@
         <v>99</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9173,13 +9193,13 @@
         <v>79</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>79</v>
@@ -9197,7 +9217,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9223,10 +9243,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9252,13 +9272,13 @@
         <v>143</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9308,7 +9328,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9323,7 +9343,7 @@
         <v>97</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>79</v>
@@ -9334,10 +9354,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9443,10 +9463,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9554,10 +9574,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9583,16 +9603,16 @@
         <v>105</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -9620,10 +9640,10 @@
         <v>156</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>79</v>
@@ -9641,7 +9661,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9656,7 +9676,7 @@
         <v>97</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>79</v>
@@ -9667,10 +9687,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9696,16 +9716,16 @@
         <v>152</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
@@ -9730,13 +9750,13 @@
         <v>79</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>79</v>
@@ -9754,7 +9774,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9769,21 +9789,21 @@
         <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9809,16 +9829,16 @@
         <v>99</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>79</v>
@@ -9831,7 +9851,7 @@
         <v>79</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>79</v>
@@ -9867,7 +9887,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9882,21 +9902,21 @@
         <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9922,13 +9942,13 @@
         <v>169</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9942,7 +9962,7 @@
         <v>79</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>79</v>
@@ -9978,7 +9998,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -9993,21 +10013,21 @@
         <v>97</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10030,13 +10050,13 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10087,7 +10107,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10102,21 +10122,21 @@
         <v>97</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10139,16 +10159,16 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10198,7 +10218,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10213,21 +10233,21 @@
         <v>97</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10253,13 +10273,13 @@
         <v>169</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10309,7 +10329,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10335,10 +10355,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10361,13 +10381,13 @@
         <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10418,7 +10438,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10433,10 +10453,10 @@
         <v>97</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>79</v>
@@ -10444,10 +10464,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10470,13 +10490,13 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10527,7 +10547,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10542,10 +10562,10 @@
         <v>97</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>79</v>
@@ -10553,10 +10573,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10579,13 +10599,13 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10636,7 +10656,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10651,25 +10671,25 @@
         <v>97</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10688,13 +10708,13 @@
         <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10745,7 +10765,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10760,10 +10780,10 @@
         <v>97</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>79</v>
@@ -10771,14 +10791,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -10797,16 +10817,16 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10856,7 +10876,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -10871,21 +10891,21 @@
         <v>97</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10908,16 +10928,16 @@
         <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10967,7 +10987,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -10982,7 +11002,7 @@
         <v>97</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>79</v>
@@ -10993,10 +11013,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11019,16 +11039,16 @@
         <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11078,7 +11098,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -11093,7 +11113,7 @@
         <v>97</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>79</v>
@@ -11104,10 +11124,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11213,10 +11233,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11324,10 +11344,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11350,16 +11370,16 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11409,7 +11429,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -11424,7 +11444,7 @@
         <v>97</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>79</v>
@@ -11435,10 +11455,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11461,13 +11481,13 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11518,7 +11538,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -11533,7 +11553,7 @@
         <v>97</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>79</v>
@@ -11544,10 +11564,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11570,13 +11590,13 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11627,7 +11647,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>86</v>
@@ -11642,7 +11662,7 @@
         <v>97</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>79</v>
@@ -11653,10 +11673,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11679,13 +11699,13 @@
         <v>79</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11736,7 +11756,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -11751,7 +11771,7 @@
         <v>97</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>79</v>
@@ -11762,10 +11782,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11871,10 +11891,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11982,14 +12002,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12011,10 +12031,10 @@
         <v>131</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>134</v>
@@ -12069,7 +12089,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12095,10 +12115,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12124,13 +12144,13 @@
         <v>152</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12156,13 +12176,13 @@
         <v>79</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>79</v>
@@ -12180,7 +12200,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12195,7 +12215,7 @@
         <v>97</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>79</v>
@@ -12206,14 +12226,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -12235,13 +12255,13 @@
         <v>152</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12270,10 +12290,10 @@
         <v>156</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
@@ -12291,7 +12311,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>86</v>
@@ -12312,15 +12332,15 @@
         <v>79</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12426,10 +12446,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12537,10 +12557,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12650,10 +12670,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12759,10 +12779,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12870,10 +12890,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12983,10 +13003,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13094,10 +13114,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13205,10 +13225,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13316,10 +13336,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13429,10 +13449,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13542,14 +13562,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -13571,13 +13591,13 @@
         <v>169</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -13627,7 +13647,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -13642,7 +13662,7 @@
         <v>97</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>79</v>
@@ -13653,10 +13673,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13679,13 +13699,13 @@
         <v>79</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13736,7 +13756,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -13751,21 +13771,21 @@
         <v>97</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13791,13 +13811,13 @@
         <v>105</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13826,10 +13846,10 @@
         <v>156</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>79</v>
@@ -13847,7 +13867,7 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -13873,10 +13893,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13902,13 +13922,13 @@
         <v>152</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -13934,13 +13954,13 @@
         <v>79</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>79</v>
@@ -13958,7 +13978,7 @@
         <v>79</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -13973,7 +13993,7 @@
         <v>97</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>79</v>
@@ -13984,10 +14004,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14010,16 +14030,16 @@
         <v>79</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14069,7 +14089,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -14084,7 +14104,7 @@
         <v>97</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>79</v>
